--- a/test/fixtures/sample.xlsx
+++ b/test/fixtures/sample.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="No Grid" sheetId="4" r:id="rId4"/>
+    <sheet name="Charts" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Q3 Budget Overview</t>
   </si>
@@ -140,6 +141,9 @@
   </si>
   <si>
     <t xml:space="preserve">support@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drawings</t>
   </si>
 </sst>
 </file>
@@ -295,6 +299,397 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:t>Q3 revenue by region</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Q3</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>Budget!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Online</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Budget!$C$3:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1385</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1060</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1598</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>802</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2650</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:crossAx val="1"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Q3</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>Budget!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Online</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Budget!$C$3:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1385</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1060</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1598</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>802</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2650</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:r>
+                  <a:t>Thousands</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:crossAx val="1"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3048000" cy="609600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 4"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="BFBFBF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Pictures, charts and text boxes</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>are drawn over the grid.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="914400" cy="457200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
@@ -52609,4 +53004,21 @@
     <mergeCell ref="B2:D2"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/test/fixtures/sample.xlsx
+++ b/test/fixtures/sample.xlsx
@@ -296,6 +296,34 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -923,6 +951,37 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B3:B8">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C8">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D9">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E8">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="season">
+      <formula>NOT(ISERROR(SEARCH("season",E3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -52963,6 +53022,19 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F2:F2001">
+    <cfRule type="top10" dxfId="1" priority="2" percent="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G2001">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 

--- a/test/fixtures/sample.xlsx
+++ b/test/fixtures/sample.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Q3 Budget Overview</t>
   </si>
@@ -141,6 +141,18 @@
   </si>
   <si>
     <t xml:space="preserve">support@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right-aligned text spills left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centered text spills to both sides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centered across B to D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A row style fills the whole row</t>
   </si>
   <si>
     <t xml:space="preserve">Drawings</t>
@@ -270,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -295,6 +307,17 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0"/>
   </cellXfs>
   <dxfs count="3">
     <dxf>
@@ -53056,6 +53079,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1" style="20"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -53069,6 +53093,28 @@
       </c>
       <c r="C4" s="15" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="F6" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+    </row>
+    <row r="12" s="19" customFormat="1">
+      <c r="B12" s="19" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -53084,7 +53130,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/test/fixtures/sample.xlsx
+++ b/test/fixtures/sample.xlsx
@@ -791,7 +791,7 @@
         <v>1385</v>
       </c>
       <c r="D3" s="5">
-        <f>C3/B3-1</f>
+        <f t="shared" ref="D3:D8" si="0">C3/B3-1</f>
         <v>0.117</v>
       </c>
       <c r="E3" t="s">
@@ -812,7 +812,7 @@
         <v>1012</v>
       </c>
       <c r="D4" s="5">
-        <f>C4/B4-1</f>
+        <f t="shared" si="0"/>
         <v>0.033</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -833,7 +833,7 @@
         <v>1060</v>
       </c>
       <c r="D5" s="5">
-        <f>C5/B5-1</f>
+        <f t="shared" si="0"/>
         <v>-0.041</v>
       </c>
       <c r="E5" t="s">
@@ -854,7 +854,7 @@
         <v>1598</v>
       </c>
       <c r="D6" s="5">
-        <f>C6/B6-1</f>
+        <f t="shared" si="0"/>
         <v>0.117</v>
       </c>
       <c r="F6" s="7">
@@ -872,7 +872,7 @@
         <v>802</v>
       </c>
       <c r="D7" s="5">
-        <f>C7/B7-1</f>
+        <f t="shared" si="0"/>
         <v>0.055</v>
       </c>
       <c r="E7" t="s">
@@ -893,7 +893,7 @@
         <v>2650</v>
       </c>
       <c r="D8" s="5">
-        <f>C8/B8-1</f>
+        <f t="shared" si="0"/>
         <v>0.199</v>
       </c>
       <c r="E8" t="s">
@@ -916,6 +916,7 @@
         <v>8507</v>
       </c>
       <c r="D9" s="5">
+        <f>C9/B9-1</f>
         <v>0.101</v>
       </c>
       <c r="E9" s="9"/>
